--- a/tests/fixtures/15_annual_budget/data-export-control.xlsx
+++ b/tests/fixtures/15_annual_budget/data-export-control.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -632,1464 +632,1465 @@
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>transaction.item</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>transaction.jan</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>transaction.feb</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>transaction.mar</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>transaction.apr</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>transaction.may</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>transaction.jun</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>transaction.jul</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>transaction.aug</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>transaction.sep</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>transaction.oct</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>transaction.nov</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>transaction.dec</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>transaction.total</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>transaction.avg</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Income 1</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>2525</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>30275</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>2522.916666666667</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Income 2</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="O8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>1010</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>12110</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R8" s="6" t="n">
         <v>1009.166666666667</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Income 3</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>252.5</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>3027.5</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>252.2916666666667</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="O10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>252.5</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>3027.5</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>252.2916666666667</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n">
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n">
         <v>4000</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="J11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="K10" s="8" t="n">
+      <c r="K11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="L11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="O11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="P11" s="8" t="n">
         <v>4040</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q11" s="8" t="n">
         <v>48440</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R11" s="8" t="n">
         <v>1009.166666666667</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>transaction.item</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>transaction.jan</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>transaction.feb</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>transaction.mar</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>transaction.apr</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>transaction.may</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>transaction.jun</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>transaction.jul</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>transaction.aug</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>transaction.sep</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>transaction.oct</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>transaction.nov</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>transaction.dec</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>transaction.total</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>transaction.avg</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Children</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>9776</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>814.6666666666666</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E15" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P15" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>1466.4</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R15" s="6" t="n">
         <v>122.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Dining</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>61.2</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>733.2000000000002</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>61.10000000000002</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="O16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q16" s="6" t="n">
+      <c r="F17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q17" s="6" t="n">
         <v>611</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R17" s="6" t="n">
         <v>50.91666666666666</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="K18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="O18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="P18" s="4" t="n">
         <v>45.9</v>
       </c>
-      <c r="Q17" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>549.8999999999999</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>45.82499999999999</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="O19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P19" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q19" s="6" t="n">
         <v>6110</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R19" s="6" t="n">
         <v>509.1666666666667</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Gifts</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>273</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="K20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="M20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="P20" s="4" t="n">
         <v>278.46</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>3336.06</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>278.0050000000001</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="M21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P21" s="6" t="n">
         <v>122.4</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q21" s="6" t="n">
         <v>1466.4</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R21" s="6" t="n">
         <v>122.2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q21" s="4" t="n">
+      <c r="F22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>611</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>50.91666666666666</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="O23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q23" s="6" t="n">
         <v>1222</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R23" s="6" t="n">
         <v>101.8333333333333</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Pets</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E24" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="K24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="O24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="P24" s="4" t="n">
         <v>79.56</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>953.1599999999999</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>79.42999999999999</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Shopping</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E25" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q24" s="6" t="n">
+      <c r="F25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q25" s="6" t="n">
         <v>611</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R25" s="6" t="n">
         <v>50.91666666666666</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E26" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="K26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="M26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P26" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>1222</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>101.8333333333333</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="M26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q26" s="6" t="n">
+      <c r="F27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q27" s="6" t="n">
         <v>611</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R27" s="6" t="n">
         <v>50.91666666666666</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="K27" s="4" t="n">
+      <c r="K28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="P28" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>122.2</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>10.18333333333334</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="M28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q28" s="6" t="n">
+      <c r="F29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q29" s="6" t="n">
         <v>611</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R29" s="6" t="n">
         <v>50.91666666666666</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E30" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="K30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="P30" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>244.4</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>20.36666666666667</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n">
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n">
         <v>2476</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="J30" s="8" t="n">
+      <c r="J31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="N30" s="8" t="n">
+      <c r="N31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="O30" s="8" t="n">
+      <c r="O31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="P30" s="8" t="n">
+      <c r="P31" s="8" t="n">
         <v>2525.52</v>
       </c>
-      <c r="Q30" s="8" t="n">
+      <c r="Q31" s="8" t="n">
         <v>30256.72</v>
       </c>
-      <c r="R30" s="8" t="n">
+      <c r="R31" s="8" t="n">
         <v>148.3172549019608</v>
       </c>
     </row>
